--- a/sources/kunimitsu_step5.xlsx
+++ b/sources/kunimitsu_step5.xlsx
@@ -774,6 +774,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>30789c48-adc1-43a6-8721-635dee152db2</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>30789c48-adc1-43a6-8721-635dee152db2</t>
@@ -826,6 +831,11 @@
           <t>Only does 20 damage if you tag.</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>49442819-bc2b-4f48-91c4-56203c67f51a</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>49442819-bc2b-4f48-91c4-56203c67f51a</t>
@@ -871,6 +881,11 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>66c176e2-e46f-45a2-84bf-6b63c3ac4a23</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -4717,6 +4732,11 @@
       <c r="K84" t="inlineStr">
         <is>
           <t>hmm"h"h"Lmhm"!</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>de1828d4-6182-4a4b-8d22-85b48de701af</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
